--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/feb-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M221"/>
+  <dimension ref="A1:M220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>24255875.73</v>
+        <v>28138.41</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6660000.16</v>
+        <v>7726.04</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1999999.76</v>
+        <v>2320.13</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1000000.73</v>
+        <v>1160.07</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>40000001.04</v>
+        <v>46402.64</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>422400</v>
+        <v>490.01</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>28109528.65</v>
+        <v>32608.91</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6448080.33</v>
+        <v>7480.2</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3801600</v>
+        <v>4410.11</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1119100.04</v>
+        <v>1298.23</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>999999.6</v>
+        <v>1160.07</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1899999.7</v>
+        <v>2204.12</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1197000.53</v>
+        <v>1388.6</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>10000000.54</v>
+        <v>11600.66</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8619729</v>
+        <v>9999.450000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1499999.4</v>
+        <v>1740.1</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4793952.24</v>
+        <v>5561.3</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>9585310.529999999</v>
+        <v>11119.59</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7634199.8</v>
+        <v>8856.17</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2999999.64995372</v>
+        <v>3480.2</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>276450.21</v>
+        <v>320.7</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1267518.86</v>
+        <v>1470.41</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7003392</v>
+        <v>8124.4</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7193399.76</v>
+        <v>8344.82</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>7054320</v>
+        <v>8183.48</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>24218539.84</v>
+        <v>28095.1</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>21666839.68</v>
+        <v>25134.96</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>109249999.48</v>
+        <v>126737.2</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>23142453.12</v>
+        <v>26846.77</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2191998.8</v>
+        <v>2542.86</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1170398.74</v>
+        <v>1357.74</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>373065</v>
+        <v>432.78</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2079298.13</v>
+        <v>2412.12</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>53333984</v>
+        <v>61870.94</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>999999.6</v>
+        <v>1160.07</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>24918500.22</v>
+        <v>28907.1</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1201849.44</v>
+        <v>1394.22</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>6537899.69</v>
+        <v>7584.39</v>
       </c>
     </row>
     <row r="40">
@@ -2883,11 +2883,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>16624999.6</v>
+        <v>19286.09</v>
       </c>
     </row>
     <row r="41">
@@ -2944,11 +2944,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>57563825.49</v>
+        <v>66777.83</v>
       </c>
     </row>
     <row r="42">
@@ -3005,11 +3005,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>52912356.11</v>
+        <v>61381.82</v>
       </c>
     </row>
     <row r="43">
@@ -3066,11 +3066,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2860000</v>
+        <v>3317.79</v>
       </c>
     </row>
     <row r="44">
@@ -3127,11 +3127,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>8478750</v>
+        <v>9835.91</v>
       </c>
     </row>
     <row r="45">
@@ -3188,11 +3188,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3735041.99</v>
+        <v>4332.89</v>
       </c>
     </row>
     <row r="46">
@@ -3249,11 +3249,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>19897750.75</v>
+        <v>23082.7</v>
       </c>
     </row>
     <row r="47">
@@ -3310,11 +3310,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>7641800.15</v>
+        <v>8864.99</v>
       </c>
     </row>
     <row r="48">
@@ -3371,11 +3371,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>367648.77</v>
+        <v>426.5</v>
       </c>
     </row>
     <row r="49">
@@ -3432,11 +3432,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>7557250.06</v>
+        <v>8766.91</v>
       </c>
     </row>
     <row r="50">
@@ -3493,11 +3493,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>866875.3100000001</v>
+        <v>1005.63</v>
       </c>
     </row>
     <row r="51">
@@ -3554,11 +3554,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>69000000.8</v>
+        <v>80044.55</v>
       </c>
     </row>
     <row r="52">
@@ -3615,11 +3615,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>11354874.27</v>
+        <v>13172.4</v>
       </c>
     </row>
     <row r="53">
@@ -3676,11 +3676,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>4000000.67</v>
+        <v>4640.26</v>
       </c>
     </row>
     <row r="54">
@@ -3737,11 +3737,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7920000</v>
+        <v>9187.719999999999</v>
       </c>
     </row>
     <row r="55">
@@ -3798,11 +3798,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>25000000.22</v>
+        <v>29001.65</v>
       </c>
     </row>
     <row r="56">
@@ -3859,11 +3859,11 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>27337252.45</v>
+        <v>31713.01</v>
       </c>
     </row>
     <row r="57">
@@ -3920,11 +3920,11 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1303398.67</v>
+        <v>1512.03</v>
       </c>
     </row>
     <row r="58">
@@ -3981,11 +3981,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>18574875.83</v>
+        <v>21548.08</v>
       </c>
     </row>
     <row r="59">
@@ -4042,11 +4042,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>13000001.61</v>
+        <v>15080.86</v>
       </c>
     </row>
     <row r="60">
@@ -4103,11 +4103,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>609899.1</v>
+        <v>707.52</v>
       </c>
     </row>
     <row r="61">
@@ -4164,11 +4164,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>608949.48</v>
+        <v>706.42</v>
       </c>
     </row>
     <row r="62">
@@ -4225,11 +4225,11 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>11410136.5</v>
+        <v>13236.51</v>
       </c>
     </row>
     <row r="63">
@@ -4286,11 +4286,11 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>749999.7</v>
+        <v>870.05</v>
       </c>
     </row>
     <row r="64">
@@ -4347,11 +4347,11 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>26433750.07</v>
+        <v>30664.89</v>
       </c>
     </row>
     <row r="65">
@@ -4408,11 +4408,11 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>15492600.36</v>
+        <v>17972.44</v>
       </c>
     </row>
     <row r="66">
@@ -4469,11 +4469,11 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>9416000</v>
+        <v>10923.18</v>
       </c>
     </row>
     <row r="67">
@@ -4530,11 +4530,11 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>20000003.35</v>
+        <v>23201.32</v>
       </c>
     </row>
     <row r="68">
@@ -4591,11 +4591,11 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>474999.92</v>
+        <v>551.03</v>
       </c>
     </row>
     <row r="69">
@@ -4652,11 +4652,11 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>34985460.28</v>
+        <v>40585.44</v>
       </c>
     </row>
     <row r="70">
@@ -4713,11 +4713,11 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>11305000</v>
+        <v>13114.54</v>
       </c>
     </row>
     <row r="71">
@@ -4774,11 +4774,11 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>21742176.2</v>
+        <v>25222.36</v>
       </c>
     </row>
     <row r="72">
@@ -4835,11 +4835,11 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2000000.33</v>
+        <v>2320.13</v>
       </c>
     </row>
     <row r="73">
@@ -4896,11 +4896,11 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>14691559.72</v>
+        <v>17043.18</v>
       </c>
     </row>
     <row r="74">
@@ -4957,11 +4957,11 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>9761401.73</v>
+        <v>11323.87</v>
       </c>
     </row>
     <row r="75">
@@ -5018,11 +5018,11 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2055493.19</v>
+        <v>2384.51</v>
       </c>
     </row>
     <row r="76">
@@ -5079,11 +5079,11 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1023152.24</v>
+        <v>1186.92</v>
       </c>
     </row>
     <row r="77">
@@ -5140,11 +5140,11 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>600000.4399999999</v>
+        <v>696.04</v>
       </c>
     </row>
     <row r="78">
@@ -5201,11 +5201,11 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>10436700.26</v>
+        <v>12107.26</v>
       </c>
     </row>
     <row r="79">
@@ -5262,11 +5262,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>14691978</v>
+        <v>17043.66</v>
       </c>
     </row>
     <row r="80">
@@ -5323,11 +5323,11 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>19950000.2</v>
+        <v>23143.31</v>
       </c>
     </row>
     <row r="81">
@@ -5384,11 +5384,11 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2400640</v>
+        <v>2784.9</v>
       </c>
     </row>
     <row r="82">
@@ -5445,11 +5445,11 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2400640</v>
+        <v>2784.9</v>
       </c>
     </row>
     <row r="83">
@@ -5506,11 +5506,11 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>37359225.39</v>
+        <v>43339.16</v>
       </c>
     </row>
     <row r="84">
@@ -5567,11 +5567,11 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>5676000</v>
+        <v>6584.53</v>
       </c>
     </row>
     <row r="85">
@@ -5628,11 +5628,11 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>13244000</v>
+        <v>15363.91</v>
       </c>
     </row>
     <row r="86">
@@ -5689,11 +5689,11 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>12307249.3</v>
+        <v>14277.22</v>
       </c>
     </row>
     <row r="87">
@@ -5750,11 +5750,11 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>17034449.74</v>
+        <v>19761.08</v>
       </c>
     </row>
     <row r="88">
@@ -5811,11 +5811,11 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>346498.25</v>
+        <v>401.96</v>
       </c>
     </row>
     <row r="89">
@@ -5872,11 +5872,11 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3599999.92</v>
+        <v>4176.24</v>
       </c>
     </row>
     <row r="90">
@@ -5933,11 +5933,11 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>7890044.8</v>
+        <v>9152.969999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5994,11 +5994,11 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>400000.48</v>
+        <v>464.03</v>
       </c>
     </row>
     <row r="92">
@@ -6055,11 +6055,11 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>13530000.36</v>
+        <v>15695.69</v>
       </c>
     </row>
     <row r="93">
@@ -6116,11 +6116,11 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1499999.4</v>
+        <v>1740.1</v>
       </c>
     </row>
     <row r="94">
@@ -6177,11 +6177,11 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>13173012.2</v>
+        <v>15281.56</v>
       </c>
     </row>
     <row r="95">
@@ -6238,11 +6238,11 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>23100000.53</v>
+        <v>26797.52</v>
       </c>
     </row>
     <row r="96">
@@ -6299,11 +6299,11 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>6600000</v>
+        <v>7656.43</v>
       </c>
     </row>
     <row r="97">
@@ -6360,11 +6360,11 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>66254499.02</v>
+        <v>76859.58</v>
       </c>
     </row>
     <row r="98">
@@ -6421,11 +6421,11 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>942000</v>
+        <v>1092.78</v>
       </c>
     </row>
     <row r="99">
@@ -6482,11 +6482,11 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>22799924</v>
+        <v>26449.41</v>
       </c>
     </row>
     <row r="100">
@@ -6543,11 +6543,11 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>8271550.32</v>
+        <v>9595.540000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6604,11 +6604,11 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>4751827.52</v>
+        <v>5512.43</v>
       </c>
     </row>
     <row r="102">
@@ -6669,11 +6669,11 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1092500000.13</v>
+        <v>1267371.99</v>
       </c>
     </row>
     <row r="103">
@@ -6730,11 +6730,11 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>23707654.45</v>
+        <v>27502.44</v>
       </c>
     </row>
     <row r="104">
@@ -6791,11 +6791,11 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>25838099.79</v>
+        <v>29973.9</v>
       </c>
     </row>
     <row r="105">
@@ -6852,11 +6852,11 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>10782822.05</v>
+        <v>12508.78</v>
       </c>
     </row>
     <row r="106">
@@ -6913,11 +6913,11 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>10069999.97</v>
+        <v>11681.86</v>
       </c>
     </row>
     <row r="107">
@@ -6974,11 +6974,11 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>10014900.53</v>
+        <v>11617.94</v>
       </c>
     </row>
     <row r="108">
@@ -7035,11 +7035,11 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>12203700.02</v>
+        <v>14157.1</v>
       </c>
     </row>
     <row r="109">
@@ -7096,11 +7096,11 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1497999.55</v>
+        <v>1737.78</v>
       </c>
     </row>
     <row r="110">
@@ -7157,11 +7157,11 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>31992675.19</v>
+        <v>37113.61</v>
       </c>
     </row>
     <row r="111">
@@ -7218,11 +7218,11 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>16553749.84</v>
+        <v>19203.44</v>
       </c>
     </row>
     <row r="112">
@@ -7279,11 +7279,11 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>999999.6</v>
+        <v>1160.07</v>
       </c>
     </row>
     <row r="113">
@@ -7340,11 +7340,11 @@
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>917999.92</v>
+        <v>1064.94</v>
       </c>
     </row>
     <row r="114">
@@ -7401,11 +7401,11 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1231824</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="115">
@@ -7462,11 +7462,11 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>8202299.79</v>
+        <v>9515.209999999999</v>
       </c>
     </row>
     <row r="116">
@@ -7523,11 +7523,11 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>7552499.7</v>
+        <v>8761.4</v>
       </c>
     </row>
     <row r="117">
@@ -7584,11 +7584,11 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>10912000.89</v>
+        <v>12658.64</v>
       </c>
     </row>
     <row r="118">
@@ -7645,11 +7645,11 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>90250.08</v>
+        <v>104.7</v>
       </c>
     </row>
     <row r="119">
@@ -7710,11 +7710,11 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>5451822.00004202</v>
+        <v>6324.47</v>
       </c>
     </row>
     <row r="120">
@@ -7771,11 +7771,11 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>21951649.93</v>
+        <v>25465.36</v>
       </c>
     </row>
     <row r="121">
@@ -7832,11 +7832,11 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>15000000.81</v>
+        <v>17400.99</v>
       </c>
     </row>
     <row r="122">
@@ -7893,11 +7893,11 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3169199.61</v>
+        <v>3676.48</v>
       </c>
     </row>
     <row r="123">
@@ -7954,11 +7954,11 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>26274149.47</v>
+        <v>30479.74</v>
       </c>
     </row>
     <row r="124">
@@ -8015,11 +8015,11 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>39901</v>
+        <v>46.29</v>
       </c>
     </row>
     <row r="125">
@@ -8076,11 +8076,11 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>5909949.9</v>
+        <v>6855.93</v>
       </c>
     </row>
     <row r="126">
@@ -8137,11 +8137,11 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1499043</v>
+        <v>1738.99</v>
       </c>
     </row>
     <row r="127">
@@ -8198,11 +8198,11 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>14546401.25</v>
+        <v>16874.78</v>
       </c>
     </row>
     <row r="128">
@@ -8259,11 +8259,11 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3219999.76</v>
+        <v>3735.41</v>
       </c>
     </row>
     <row r="129">
@@ -8320,11 +8320,11 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3230105.12</v>
+        <v>3747.13</v>
       </c>
     </row>
     <row r="130">
@@ -8381,11 +8381,11 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>14579650.39</v>
+        <v>16913.36</v>
       </c>
     </row>
     <row r="131">
@@ -8442,11 +8442,11 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>298300.51</v>
+        <v>346.05</v>
       </c>
     </row>
     <row r="132">
@@ -8503,11 +8503,11 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>21546570.3</v>
+        <v>24995.44</v>
       </c>
     </row>
     <row r="133">
@@ -8564,11 +8564,11 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>165001132.66</v>
+        <v>191412.19</v>
       </c>
     </row>
     <row r="134">
@@ -8625,11 +8625,11 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>60953899.93</v>
+        <v>70710.53999999999</v>
       </c>
     </row>
     <row r="135">
@@ -8686,11 +8686,11 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>453330.5</v>
+        <v>525.89</v>
       </c>
     </row>
     <row r="136">
@@ -8747,11 +8747,11 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2486396.83</v>
+        <v>2884.38</v>
       </c>
     </row>
     <row r="137">
@@ -8808,11 +8808,11 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1506490.73</v>
+        <v>1747.63</v>
       </c>
     </row>
     <row r="138">
@@ -8869,11 +8869,11 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>9631100.300000001</v>
+        <v>11172.71</v>
       </c>
     </row>
     <row r="139">
@@ -8930,11 +8930,11 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>999999.6</v>
+        <v>1160.07</v>
       </c>
     </row>
     <row r="140">
@@ -8991,11 +8991,11 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>999999.6</v>
+        <v>1160.07</v>
       </c>
     </row>
     <row r="141">
@@ -9052,11 +9052,11 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>4000000.67</v>
+        <v>4640.26</v>
       </c>
     </row>
     <row r="142">
@@ -9113,11 +9113,11 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>16787925</v>
+        <v>19475.1</v>
       </c>
     </row>
     <row r="143">
@@ -9174,11 +9174,11 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>5035949.04</v>
+        <v>5842.03</v>
       </c>
     </row>
     <row r="144">
@@ -9239,11 +9239,11 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>95509320.27</v>
+        <v>110797.1</v>
       </c>
     </row>
     <row r="145">
@@ -9300,11 +9300,11 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1999999.2</v>
+        <v>2320.13</v>
       </c>
     </row>
     <row r="146">
@@ -9361,11 +9361,11 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>11172000.07</v>
+        <v>12960.26</v>
       </c>
     </row>
     <row r="147">
@@ -9422,11 +9422,11 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>12041059.51</v>
+        <v>13968.42</v>
       </c>
     </row>
     <row r="148">
@@ -9483,11 +9483,11 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>8025599.25</v>
+        <v>9310.219999999999</v>
       </c>
     </row>
     <row r="149">
@@ -9544,11 +9544,11 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>778999.29</v>
+        <v>903.6900000000001</v>
       </c>
     </row>
     <row r="150">
@@ -9605,11 +9605,11 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>20000001.08</v>
+        <v>23201.32</v>
       </c>
     </row>
     <row r="151">
@@ -9666,11 +9666,11 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>13998981.5</v>
+        <v>16239.74</v>
       </c>
     </row>
     <row r="152">
@@ -9727,11 +9727,11 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>859863.95</v>
+        <v>997.5</v>
       </c>
     </row>
     <row r="153">
@@ -9788,11 +9788,11 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>15033600.4</v>
+        <v>17439.97</v>
       </c>
     </row>
     <row r="154">
@@ -9849,11 +9849,11 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>5878600</v>
+        <v>6819.56</v>
       </c>
     </row>
     <row r="155">
@@ -9910,11 +9910,11 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>200000.24</v>
+        <v>232.01</v>
       </c>
     </row>
     <row r="156">
@@ -9971,11 +9971,11 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>32290650.12</v>
+        <v>37459.28</v>
       </c>
     </row>
     <row r="157">
@@ -10032,11 +10032,11 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1220940</v>
+        <v>1416.37</v>
       </c>
     </row>
     <row r="158">
@@ -10093,11 +10093,11 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>65000000.13</v>
+        <v>75404.28</v>
       </c>
     </row>
     <row r="159">
@@ -10154,11 +10154,11 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>35522399.16</v>
+        <v>41208.32</v>
       </c>
     </row>
     <row r="160">
@@ -10215,11 +10215,11 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>13501399.84</v>
+        <v>15662.51</v>
       </c>
     </row>
     <row r="161">
@@ -10276,11 +10276,11 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>8842499.68</v>
+        <v>10257.88</v>
       </c>
     </row>
     <row r="162">
@@ -10337,11 +10337,11 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>6405600</v>
+        <v>7430.92</v>
       </c>
     </row>
     <row r="163">
@@ -10398,11 +10398,11 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>6625208.48</v>
+        <v>7685.68</v>
       </c>
     </row>
     <row r="164">
@@ -10459,11 +10459,11 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>17000000.02</v>
+        <v>19721.12</v>
       </c>
     </row>
     <row r="165">
@@ -10520,11 +10520,11 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>15827000</v>
+        <v>18360.36</v>
       </c>
     </row>
     <row r="166">
@@ -10581,11 +10581,11 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>34980899.84</v>
+        <v>40580.15</v>
       </c>
     </row>
     <row r="167">
@@ -10642,11 +10642,11 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>354000.25</v>
+        <v>410.66</v>
       </c>
     </row>
     <row r="168">
@@ -10703,11 +10703,11 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>924000</v>
+        <v>1071.9</v>
       </c>
     </row>
     <row r="169">
@@ -10764,11 +10764,11 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>150000.39</v>
+        <v>174.01</v>
       </c>
     </row>
     <row r="170">
@@ -10825,11 +10825,11 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>10110177.94</v>
+        <v>11728.47</v>
       </c>
     </row>
     <row r="171">
@@ -10886,11 +10886,11 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3153998.91</v>
+        <v>3658.85</v>
       </c>
     </row>
     <row r="172">
@@ -10947,11 +10947,11 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>11721600</v>
+        <v>13597.83</v>
       </c>
     </row>
     <row r="173">
@@ -11008,11 +11008,11 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>579025.14</v>
+        <v>671.71</v>
       </c>
     </row>
     <row r="174">
@@ -11069,11 +11069,11 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>47000000.51</v>
+        <v>54523.1</v>
       </c>
     </row>
     <row r="175">
@@ -11130,11 +11130,11 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>30909580.45</v>
+        <v>35857.15</v>
       </c>
     </row>
     <row r="176">
@@ -11191,11 +11191,11 @@
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>8717199.58</v>
+        <v>10112.53</v>
       </c>
     </row>
     <row r="177">
@@ -11252,11 +11252,11 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>13395000.57</v>
+        <v>15539.08</v>
       </c>
     </row>
     <row r="178">
@@ -11313,11 +11313,11 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>4377600.1</v>
+        <v>5078.3</v>
       </c>
     </row>
     <row r="179">
@@ -11374,11 +11374,11 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>12000000.88</v>
+        <v>13920.79</v>
       </c>
     </row>
     <row r="180">
@@ -11435,11 +11435,11 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>7028387.52</v>
+        <v>8153.39</v>
       </c>
     </row>
     <row r="181">
@@ -11496,11 +11496,11 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>5500800.47</v>
+        <v>6381.29</v>
       </c>
     </row>
     <row r="182">
@@ -11561,11 +11561,11 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>472412199.98</v>
+        <v>548029.28</v>
       </c>
     </row>
     <row r="183">
@@ -11622,11 +11622,11 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>20000001.08</v>
+        <v>23201.32</v>
       </c>
     </row>
     <row r="184">
@@ -11683,11 +11683,11 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1350000.14</v>
+        <v>1566.09</v>
       </c>
     </row>
     <row r="185">
@@ -11744,11 +11744,11 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>18002750.13</v>
+        <v>20884.38</v>
       </c>
     </row>
     <row r="186">
@@ -11805,11 +11805,11 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>11500463.45</v>
+        <v>13341.3</v>
       </c>
     </row>
     <row r="187">
@@ -11866,11 +11866,11 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>30020000.17</v>
+        <v>34825.18</v>
       </c>
     </row>
     <row r="188">
@@ -11927,11 +11927,11 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>8825025.539999999</v>
+        <v>10237.61</v>
       </c>
     </row>
     <row r="189">
@@ -11988,11 +11988,11 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>28864000</v>
+        <v>33484.14</v>
       </c>
     </row>
     <row r="190">
@@ -12049,11 +12049,11 @@
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>428450.46</v>
+        <v>497.03</v>
       </c>
     </row>
     <row r="191">
@@ -12110,11 +12110,11 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>26326305.09</v>
+        <v>30540.25</v>
       </c>
     </row>
     <row r="192">
@@ -12171,11 +12171,11 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>8478750</v>
+        <v>9835.91</v>
       </c>
     </row>
     <row r="193">
@@ -12232,11 +12232,11 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>18230499.53</v>
+        <v>21148.58</v>
       </c>
     </row>
     <row r="194">
@@ -12293,11 +12293,11 @@
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>45285881.02</v>
+        <v>52534.61</v>
       </c>
     </row>
     <row r="195">
@@ -12354,11 +12354,11 @@
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>17099999.53</v>
+        <v>19837.13</v>
       </c>
     </row>
     <row r="196">
@@ -12415,17 +12415,17 @@
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>41557222.96</v>
+        <v>48209.12</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>952946-21-CM26</t>
+          <t>5349-427-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12450,17 +12450,17 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12476,17 +12476,17 @@
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1999999.76004628</v>
+        <v>61658.5</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5349-427-CM26</t>
+          <t>952946-21-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12511,17 +12511,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>Jefatura Adm y log Campo Militar Valdivia</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12537,11 +12537,11 @@
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>53150858.83</v>
+        <v>2320.13</v>
       </c>
     </row>
     <row r="199">
@@ -12598,11 +12598,11 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>36299024.4</v>
+        <v>42109.26</v>
       </c>
     </row>
     <row r="200">
@@ -12659,17 +12659,17 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>11305000</v>
+        <v>13114.54</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>5052-147-SE26</t>
+          <t>2021-8-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12694,17 +12694,17 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>Estado Mayor Conjunto</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12724,11 +12724,11 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>261159175.48</v>
+        <v>242167.23</v>
       </c>
     </row>
     <row r="202">
@@ -12785,11 +12785,11 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>5315211.93</v>
+        <v>6166</v>
       </c>
     </row>
     <row r="203">
@@ -12846,11 +12846,11 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>32075421.01</v>
+        <v>37209.6</v>
       </c>
     </row>
     <row r="204">
@@ -12907,11 +12907,11 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>1889981.21</v>
+        <v>2192.5</v>
       </c>
     </row>
     <row r="205">
@@ -12968,17 +12968,17 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>5298000.07</v>
+        <v>6146.03</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2021-8-CM26</t>
+          <t>5052-147-SE26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13003,17 +13003,17 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13033,11 +13033,11 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>208752999.91</v>
+        <v>302961.85</v>
       </c>
     </row>
     <row r="207">
@@ -13094,11 +13094,11 @@
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>52249999.55</v>
+        <v>60613.44</v>
       </c>
     </row>
     <row r="208">
@@ -13155,11 +13155,11 @@
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>43429249.56</v>
+        <v>50380.79</v>
       </c>
     </row>
     <row r="209">
@@ -13216,11 +13216,11 @@
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>8000000.21</v>
+        <v>9280.530000000001</v>
       </c>
     </row>
     <row r="210">
@@ -13277,11 +13277,11 @@
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>28262500</v>
+        <v>32786.36</v>
       </c>
     </row>
     <row r="211">
@@ -13338,11 +13338,11 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>30021900.54</v>
+        <v>34827.38</v>
       </c>
     </row>
     <row r="212">
@@ -13399,17 +13399,17 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1277939.81</v>
+        <v>1482.49</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1099899-50-CM26</t>
+          <t>2170-185-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13434,12 +13434,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13460,17 +13460,17 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>6324720.17</v>
+        <v>4924.57</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2170-185-CM26</t>
+          <t>1079454-49-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13490,22 +13490,22 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13521,17 +13521,17 @@
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>4245074.98</v>
+        <v>1361.05</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1005498-24-CM26</t>
+          <t>2170-184-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13551,22 +13551,22 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>60.810.000-8</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>COMISION PARA EL MERCADO FINANCIERO</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13582,17 +13582,17 @@
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>45375032.56</v>
+        <v>385.72</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2170-184-CM26</t>
+          <t>2170-183-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13643,17 +13643,17 @@
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>332500.4</v>
+        <v>3857.22</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2170-183-CM26</t>
+          <t>2170-182-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13704,17 +13704,17 @@
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>3324999.47</v>
+        <v>25639.49</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2170-182-CM26</t>
+          <t>1077908-39-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13734,22 +13734,22 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13765,17 +13765,17 @@
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>22101750.94</v>
+        <v>36669.63</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1077908-39-CM26</t>
+          <t>1099899-50-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13795,22 +13795,22 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13826,17 +13826,17 @@
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>31609954.59</v>
+        <v>7337.09</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1079454-49-CM26</t>
+          <t>617807-1211-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13856,22 +13856,22 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13887,72 +13887,11 @@
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>1173249.86</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>617807-1211-CM26</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>2239-13-LR23</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>feb-2026</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>61.602.036-6</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M221" s="2" t="n">
-        <v>17126001.03</v>
+        <v>19867.29</v>
       </c>
     </row>
   </sheetData>
